--- a/docs/database/人间烟火_数据库设计文档.xlsx
+++ b/docs/database/人间烟火_数据库设计文档.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="18360" activeTab="4"/>
+    <workbookView windowHeight="18360" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="用户管理" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="363">
   <si>
     <t>用户管理</t>
   </si>
@@ -70,6 +70,15 @@
     <t/>
   </si>
   <si>
+    <t>user_id</t>
+  </si>
+  <si>
+    <t>VARCHAR(255)</t>
+  </si>
+  <si>
+    <t>唯一字段</t>
+  </si>
+  <si>
     <t>username</t>
   </si>
   <si>
@@ -100,9 +109,6 @@
     <t>password_hash</t>
   </si>
   <si>
-    <t>VARCHAR(255)</t>
-  </si>
-  <si>
     <t>密码哈希</t>
   </si>
   <si>
@@ -232,6 +238,12 @@
     <t>百科菜谱信息（encyclopedia_recipes）</t>
   </si>
   <si>
+    <t>encyclopedia_recipes_id</t>
+  </si>
+  <si>
+    <t>百科菜谱id</t>
+  </si>
+  <si>
     <t>name</t>
   </si>
   <si>
@@ -349,7 +361,7 @@
     <t>NOT NULL, DEFAULT 0</t>
   </si>
   <si>
-    <t>每次获取详情时自动 +1</t>
+    <t>每次获取详情时自动 +1,用于做推荐算法</t>
   </si>
   <si>
     <t>idx_encyclopedia_name</t>
@@ -388,7 +400,18 @@
     <t>JSON 字段结构说明</t>
   </si>
   <si>
-    <t>▶ ingredients / process_steps 子字段（Ingredient / ProcessStep 结构体）</t>
+    <r>
+      <t>▶</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> ingredients / process_steps 子字段（Ingredient / ProcessStep 结构体）</t>
+    </r>
   </si>
   <si>
     <t>子字段名</t>
@@ -485,9 +508,6 @@
   </si>
   <si>
     <t>我的菜谱主表（my_recipes）</t>
-  </si>
-  <si>
-    <t>user_id</t>
   </si>
   <si>
     <t>所属用户 ID</t>
@@ -1124,7 +1144,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1165,6 +1185,12 @@
     <font>
       <sz val="10"/>
       <name val="Consolas"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1685,148 +1711,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1874,7 +1900,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2224,7 +2250,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -2293,198 +2319,194 @@
       <c r="C8" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+    </row>
+    <row r="9" ht="20" customHeight="1" spans="1:5">
+      <c r="A9" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="B9" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="9" ht="20" customHeight="1" spans="1:5">
-      <c r="A9" s="13" t="s">
+    <row r="10" ht="20" customHeight="1" spans="1:5">
+      <c r="A10" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1" spans="1:5">
+      <c r="A11" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1" spans="1:5">
+      <c r="A12" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1" spans="1:5">
-      <c r="A10" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1" spans="1:5">
-      <c r="A11" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E11" s="8" t="s">
+      <c r="C12" s="8" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="12" ht="20" customHeight="1" spans="1:5">
-      <c r="A12" s="14" t="s">
+      <c r="D12" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="E12" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C12" s="12" t="s">
+    </row>
+    <row r="13" ht="20" customHeight="1" spans="1:5">
+      <c r="A13" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="B13" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="C13" s="12" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="13" ht="20" customHeight="1" spans="1:5">
-      <c r="A13" s="13" t="s">
+      <c r="D13" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="E13" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="8" t="s">
+    </row>
+    <row r="14" ht="20" customHeight="1" spans="1:5">
+      <c r="A14" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="B14" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="C14" s="8" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="14" ht="20" customHeight="1" spans="1:5">
-      <c r="A14" s="14" t="s">
+      <c r="D14" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="14" t="s">
+      <c r="E14" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="12" t="s">
+    </row>
+    <row r="15" ht="20" customHeight="1" spans="1:5">
+      <c r="A15" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="B15" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="C15" s="12" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="15" ht="20" customHeight="1" spans="1:5">
-      <c r="A15" s="13" t="s">
+      <c r="D15" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="C15" s="8" t="s">
+      <c r="E15" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="D15" s="8" t="s">
+    </row>
+    <row r="16" ht="20" customHeight="1" spans="1:5">
+      <c r="A16" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="B16" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" s="8" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="16" ht="20" customHeight="1" spans="1:5">
-      <c r="A16" s="14" t="s">
+      <c r="D16" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="B16" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="C16" s="12" t="s">
+      <c r="E16" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="D16" s="12" t="s">
+    </row>
+    <row r="17" ht="20" customHeight="1" spans="1:5">
+      <c r="A17" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="E16" s="12" t="s">
+      <c r="B17" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" s="12" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="19" ht="18" spans="1:5">
-      <c r="A19" s="2" t="s">
+      <c r="D17" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-    </row>
-    <row r="20" ht="16.5" spans="1:5">
-      <c r="A20" s="6" t="s">
+      <c r="E17" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="B20" s="6" t="s">
+    </row>
+    <row r="20" ht="18" spans="1:5">
+      <c r="A20" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+    </row>
+    <row r="21" ht="16.5" spans="1:5">
+      <c r="A21" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B21" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C20" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="D20" s="6" t="s">
+      <c r="C21" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D21" s="6" t="s">
         <v>4</v>
-      </c>
-    </row>
-    <row r="21" ht="16.5" spans="1:5">
-      <c r="A21" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="B21" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="C21" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="D21" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="E21" s="17" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:5">
       <c r="A22" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="B22" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="B22" s="14" t="s">
-        <v>57</v>
-      </c>
       <c r="C22" s="14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D22" s="14" t="s">
         <v>60</v>
@@ -2498,22 +2520,39 @@
         <v>61</v>
       </c>
       <c r="B23" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="C23" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="D23" s="14" t="s">
+      <c r="E23" s="17" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" ht="16.5" spans="1:5">
+      <c r="A24" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="E23" s="17" t="s">
+      <c r="B24" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="E24" s="17" t="s">
         <v>11</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A20:E20"/>
     <mergeCell ref="A1:E2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2524,7 +2563,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -2536,13 +2575,13 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1"/>
     <row r="5" ht="24" customHeight="1" spans="1:5">
       <c r="A5" s="16" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -2585,277 +2624,273 @@
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:5">
       <c r="A8" s="14" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="E8" s="12" t="s">
         <v>69</v>
       </c>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:5">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="D9" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="E9" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1" spans="1:5">
+      <c r="A10" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1" spans="1:5">
+      <c r="A11" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="B11" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="E9" s="8" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1" spans="1:5">
-      <c r="A10" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="B10" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1" spans="1:5">
-      <c r="A11" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="E11" s="8" t="s">
+      <c r="C11" s="12" t="s">
         <v>79</v>
       </c>
+      <c r="D11" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:5">
-      <c r="A12" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="B12" s="14" t="s">
+      <c r="A12" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="B12" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="D12" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="E12" s="12" t="s">
+      <c r="D12" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" s="8" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:5">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="B13" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="C13" s="8" t="s">
+      <c r="B13" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="D13" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E13" s="8" t="s">
+      <c r="C13" s="12" t="s">
         <v>86</v>
       </c>
+      <c r="D13" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:5">
-      <c r="A14" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="B14" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="C14" s="12" t="s">
+      <c r="A14" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="D14" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="E14" s="12" t="s">
+      <c r="B14" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="C14" s="8" t="s">
         <v>89</v>
       </c>
+      <c r="D14" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:5">
-      <c r="A15" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" s="8" t="s">
+      <c r="A15" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="D15" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="E15" s="8" t="s">
+      <c r="B15" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="C15" s="12" t="s">
         <v>92</v>
       </c>
+      <c r="D15" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:5">
-      <c r="A16" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="B16" s="14" t="s">
+      <c r="A16" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="B16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E16" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="E16" s="12" t="s">
+    </row>
+    <row r="17" ht="20" customHeight="1" spans="1:5">
+      <c r="A17" s="14" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="17" ht="20" customHeight="1" spans="1:5">
-      <c r="A17" s="13" t="s">
+      <c r="B17" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="B17" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="D17" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="E17" s="8" t="s">
+      <c r="D17" s="12" t="s">
         <v>100</v>
       </c>
+      <c r="E17" s="12" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:5">
-      <c r="A18" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="B18" s="14" t="s">
+      <c r="A18" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="B18" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E18" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="E18" s="12" t="s">
+    </row>
+    <row r="19" ht="20" customHeight="1" spans="1:5">
+      <c r="A19" s="14" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="19" ht="20" customHeight="1" spans="1:5">
-      <c r="A19" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="C19" s="8" t="s">
+      <c r="B19" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1" spans="1:5">
+      <c r="A20" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="B20" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="C20" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E20" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="20" ht="20" customHeight="1" spans="1:5">
-      <c r="A20" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="B20" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="D20" s="12" t="s">
+    <row r="21" ht="20" customHeight="1" spans="1:5">
+      <c r="A21" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="E20" s="12" t="s">
+      <c r="B21" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="E21" s="12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="23" ht="18" spans="1:5">
-      <c r="A23" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-    </row>
-    <row r="24" ht="16.5" spans="1:5">
-      <c r="A24" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B24" s="6" t="s">
+    <row r="24" ht="18" spans="1:5">
+      <c r="A24" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+    </row>
+    <row r="25" ht="16.5" spans="1:5">
+      <c r="A25" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B25" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C24" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="D24" s="6" t="s">
+      <c r="C25" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D25" s="6" t="s">
         <v>4</v>
-      </c>
-    </row>
-    <row r="25" ht="16.5" spans="1:5">
-      <c r="A25" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="B25" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="C25" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="D25" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="E25" s="17" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="26" ht="16.5" spans="1:5">
       <c r="A26" s="14" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E26" s="17" t="s">
         <v>11</v>
@@ -2863,16 +2898,16 @@
     </row>
     <row r="27" ht="16.5" spans="1:5">
       <c r="A27" s="14" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E27" s="17" t="s">
         <v>11</v>
@@ -2880,10 +2915,10 @@
     </row>
     <row r="28" ht="16.5" spans="1:5">
       <c r="A28" s="14" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B28" s="14" t="s">
-        <v>114</v>
+        <v>59</v>
       </c>
       <c r="C28" s="14" t="s">
         <v>115</v>
@@ -2895,66 +2930,66 @@
         <v>11</v>
       </c>
     </row>
-    <row r="31" ht="18" spans="1:5">
-      <c r="A31" s="2" t="s">
+    <row r="29" ht="16.5" spans="1:5">
+      <c r="A29" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
-    </row>
-    <row r="32" ht="16.5" spans="1:5">
-      <c r="A32" s="19" t="s">
+      <c r="B29" s="14" t="s">
         <v>118</v>
       </c>
+      <c r="C29" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="E29" s="17" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" ht="18" spans="1:5">
+      <c r="A32" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
     </row>
     <row r="33" ht="16.5" spans="1:5">
-      <c r="A33" s="20" t="s">
-        <v>119</v>
-      </c>
-      <c r="B33" s="20" t="s">
+      <c r="A33" s="19" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="34" ht="16.5" spans="1:5">
+      <c r="A34" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="B34" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="C33" s="20" t="s">
+      <c r="C34" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="D33" s="20" t="s">
-        <v>120</v>
-      </c>
-      <c r="E33" s="20" t="s">
+      <c r="D34" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="E34" s="20" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="34" ht="16.5" spans="1:5">
-      <c r="A34" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="B34" s="14" t="s">
-        <v>121</v>
-      </c>
-      <c r="C34" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="D34" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="E34" s="14" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="35" ht="16.5" spans="1:5">
       <c r="A35" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="B35" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="B35" s="14" t="s">
+      <c r="C35" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="C35" s="14" t="s">
+      <c r="D35" s="14" t="s">
         <v>127</v>
-      </c>
-      <c r="D35" s="14" t="s">
-        <v>123</v>
       </c>
       <c r="E35" s="14" t="s">
         <v>128</v>
@@ -2965,49 +3000,49 @@
         <v>129</v>
       </c>
       <c r="B36" s="14" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="E36" s="14" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="37" ht="16.5" spans="1:5">
       <c r="A37" s="14" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B37" s="14" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D37" s="14" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="E37" s="14" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="39" ht="16.5" spans="1:5">
-      <c r="A39" s="14" t="s">
+    <row r="38" ht="16.5" spans="1:5">
+      <c r="A38" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="B39" s="14" t="s">
+      <c r="B38" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="C38" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="C39" s="14" t="s">
+      <c r="D38" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="D39" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="E39" s="14" t="s">
+      <c r="E38" s="14" t="s">
         <v>139</v>
       </c>
     </row>
@@ -3016,58 +3051,75 @@
         <v>140</v>
       </c>
       <c r="B40" s="14" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="E40" s="14" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="41" ht="16.5" spans="1:5">
       <c r="A41" s="14" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B41" s="14" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C41" s="14" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D41" s="14" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="E41" s="14" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="42" ht="16.5" spans="1:5">
       <c r="A42" s="14" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B42" s="14" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D42" s="14" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E42" s="14" t="s">
-        <v>148</v>
+        <v>149</v>
+      </c>
+    </row>
+    <row r="43" ht="16.5" spans="1:5">
+      <c r="A43" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="B43" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="C43" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="D43" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="E43" s="14" t="s">
+        <v>152</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A24:E24"/>
     <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A33:E33"/>
     <mergeCell ref="A1:E2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3090,13 +3142,13 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1"/>
     <row r="5" ht="24" customHeight="1" spans="1:5">
       <c r="A5" s="16" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -3139,118 +3191,118 @@
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:5">
       <c r="A8" s="14" t="s">
-        <v>151</v>
+        <v>12</v>
       </c>
       <c r="B8" s="14" t="s">
         <v>8</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:5">
       <c r="A9" s="13" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:5">
       <c r="A10" s="14" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B10" s="14" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:5">
       <c r="A11" s="13" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:5">
       <c r="A12" s="14" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:5">
       <c r="A13" s="13" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>8</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:5">
       <c r="A14" s="14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E14" s="12" t="s">
         <v>11</v>
@@ -3258,16 +3310,16 @@
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:5">
       <c r="A15" s="13" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E15" s="8" t="s">
         <v>11</v>
@@ -3275,24 +3327,24 @@
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:5">
       <c r="A16" s="14" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:5">
       <c r="A19" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -3301,13 +3353,13 @@
     </row>
     <row r="20" ht="16.5" spans="1:5">
       <c r="A20" s="6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>4</v>
@@ -3315,16 +3367,16 @@
     </row>
     <row r="21" ht="16.5" spans="1:5">
       <c r="A21" s="14" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>151</v>
+        <v>12</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E21" s="17" t="s">
         <v>11</v>
@@ -3332,16 +3384,16 @@
     </row>
     <row r="22" ht="16.5" spans="1:5">
       <c r="A22" s="14" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E22" s="17" t="s">
         <v>11</v>
@@ -3349,16 +3401,16 @@
     </row>
     <row r="23" ht="16.5" spans="1:5">
       <c r="A23" s="14" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E23" s="17" t="s">
         <v>11</v>
@@ -3366,16 +3418,16 @@
     </row>
     <row r="24" ht="16.5" spans="1:5">
       <c r="A24" s="14" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E24" s="17" t="s">
         <v>11</v>
@@ -3383,16 +3435,16 @@
     </row>
     <row r="25" ht="33" spans="1:5">
       <c r="A25" s="14" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E25" s="17" t="s">
         <v>11</v>
@@ -3400,7 +3452,7 @@
     </row>
     <row r="28" ht="16.5" spans="1:5">
       <c r="A28" s="18" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
@@ -3409,32 +3461,32 @@
     </row>
     <row r="29" ht="16.5" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="30" ht="16.5" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="31" ht="16.5" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="32" ht="16.5" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="33" ht="16.5" spans="1:1">
       <c r="A33" s="5" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="34" ht="16.5" spans="1:1">
       <c r="A34" s="5" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>
@@ -3470,13 +3522,13 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1"/>
     <row r="5" ht="24" customHeight="1" spans="1:5">
       <c r="A5" s="16" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -3514,148 +3566,148 @@
         <v>10</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:5">
       <c r="A8" s="14" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B8" s="14" t="s">
         <v>8</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:5">
       <c r="A9" s="13" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:5">
       <c r="A10" s="14" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:5">
       <c r="A11" s="13" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:5">
       <c r="A12" s="14" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:5">
       <c r="A13" s="13" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:5">
       <c r="A14" s="14" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:5">
       <c r="A15" s="13" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:5">
       <c r="A18" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -3664,13 +3716,13 @@
     </row>
     <row r="19" ht="16.5" spans="1:5">
       <c r="A19" s="6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>4</v>
@@ -3678,16 +3730,16 @@
     </row>
     <row r="20" ht="16.5" spans="1:5">
       <c r="A20" s="14" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="E20" s="17" t="s">
         <v>11</v>
@@ -3695,16 +3747,16 @@
     </row>
     <row r="21" ht="33" spans="1:5">
       <c r="A21" s="14" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="E21" s="17" t="s">
         <v>11</v>
@@ -3712,16 +3764,16 @@
     </row>
     <row r="22" ht="33" spans="1:5">
       <c r="A22" s="14" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E22" s="17" t="s">
         <v>11</v>
@@ -3729,7 +3781,7 @@
     </row>
     <row r="25" ht="16.5" spans="1:5">
       <c r="A25" s="18" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -3738,37 +3790,37 @@
     </row>
     <row r="26" ht="16.5" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="27" ht="16.5" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="28" ht="16.5" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="29" ht="16.5" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="30" ht="16.5" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="31" ht="16.5" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="32" ht="16.5" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
   </sheetData>
@@ -3798,13 +3850,13 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1"/>
     <row r="5" ht="18" spans="1:5">
       <c r="A5" s="2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -3813,92 +3865,92 @@
     </row>
     <row r="6" ht="33" spans="1:5">
       <c r="A6" s="6" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:5">
       <c r="A7" s="13" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>151</v>
+        <v>12</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:5">
       <c r="A8" s="14" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:5">
       <c r="A9" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="B9" s="13" t="s">
         <v>240</v>
       </c>
-      <c r="B9" s="13" t="s">
-        <v>237</v>
-      </c>
       <c r="C9" s="13" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:5">
       <c r="A10" s="14" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:5">
       <c r="A13" s="2" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -3912,107 +3964,107 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="15" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="15" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="15" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="15" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="15" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="15" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="15" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="15" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="15" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="15" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="15" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="15" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="15" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="15" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="15" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="15" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="15" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="15" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="15" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="15" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="15" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="36" ht="16.5" spans="1:5">
@@ -4022,7 +4074,7 @@
     </row>
     <row r="39" ht="18" spans="1:5">
       <c r="A39" s="2" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -4031,92 +4083,92 @@
     </row>
     <row r="40" ht="33" spans="1:5">
       <c r="A40" s="6" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="41" ht="36" customHeight="1" spans="1:5">
       <c r="A41" s="8" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="42" ht="36" customHeight="1" spans="1:5">
       <c r="A42" s="12" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C42" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="D42" s="12" t="s">
         <v>281</v>
       </c>
-      <c r="D42" s="12" t="s">
-        <v>278</v>
-      </c>
       <c r="E42" s="12" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="43" ht="36" customHeight="1" spans="1:5">
       <c r="A43" s="8" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="44" ht="36" customHeight="1" spans="1:5">
       <c r="A44" s="12" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="47" ht="18" spans="1:5">
       <c r="A47" s="2" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
@@ -4130,167 +4182,167 @@
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="15" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="15" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="15" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="15" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="15" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="15" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="15" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="15" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="15" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="15" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="15" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="15" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="15" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="15" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="15" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="15" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="15" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="15" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="15" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="15" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="15" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="15" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="15" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="15" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="15" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="15" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="15" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="15" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="15" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="15" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="15" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="15" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="15" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="82" spans="1:1">
@@ -4382,12 +4434,12 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:5">
       <c r="A5" s="2" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -4396,57 +4448,57 @@
     </row>
     <row r="6" ht="16.5" spans="1:5">
       <c r="A6" s="4" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="7" ht="40" customHeight="1" spans="1:5">
       <c r="A7" s="5" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:5">
       <c r="A8" s="4" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="9" ht="40" customHeight="1" spans="1:5">
       <c r="A9" s="5" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:5">
       <c r="A10" s="4" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11" ht="40" customHeight="1" spans="1:5">
       <c r="A11" s="5" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:5">
       <c r="A12" s="4" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="13" ht="40" customHeight="1" spans="1:5">
       <c r="A13" s="5" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:5">
       <c r="A14" s="4" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="15" ht="40" customHeight="1" spans="1:5">
       <c r="A15" s="5" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:5">
       <c r="A18" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -4455,77 +4507,77 @@
     </row>
     <row r="19" ht="16.5" spans="1:5">
       <c r="A19" s="4" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="20" ht="50" customHeight="1" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:5">
       <c r="A21" s="4" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="22" ht="50" customHeight="1" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:5">
       <c r="A23" s="4" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="24" ht="50" customHeight="1" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="25" ht="16.5" spans="1:5">
       <c r="A25" s="4" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="26" ht="50" customHeight="1" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="27" ht="16.5" spans="1:5">
       <c r="A27" s="4" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="28" ht="50" customHeight="1" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="29" ht="16.5" spans="1:5">
       <c r="A29" s="4" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="30" ht="50" customHeight="1" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="31" ht="16.5" spans="1:5">
       <c r="A31" s="4" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="32" ht="50" customHeight="1" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="35" ht="18" spans="1:5">
       <c r="A35" s="2" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -4534,81 +4586,81 @@
     </row>
     <row r="36" ht="16.5" spans="1:5">
       <c r="A36" s="6" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="37" ht="36" customHeight="1" spans="1:5">
       <c r="A37" s="7" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="10"/>
     </row>
     <row r="38" ht="36" customHeight="1" spans="1:5">
       <c r="A38" s="11" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C38" s="9"/>
       <c r="D38" s="10"/>
     </row>
     <row r="39" ht="36" customHeight="1" spans="1:5">
       <c r="A39" s="7" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="10"/>
     </row>
     <row r="40" ht="36" customHeight="1" spans="1:5">
       <c r="A40" s="11" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="C40" s="9"/>
       <c r="D40" s="10"/>
     </row>
     <row r="41" ht="36" customHeight="1" spans="1:5">
       <c r="A41" s="7" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="10"/>
     </row>
     <row r="42" ht="36" customHeight="1" spans="1:5">
       <c r="A42" s="11" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="C42" s="9"/>
       <c r="D42" s="10"/>
     </row>
     <row r="43" ht="36" customHeight="1" spans="1:5">
       <c r="A43" s="7" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="10"/>

--- a/docs/database/人间烟火_数据库设计文档.xlsx
+++ b/docs/database/人间烟火_数据库设计文档.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="18360" activeTab="1"/>
+    <workbookView windowHeight="18360" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="用户管理" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="365">
   <si>
     <t>用户管理</t>
   </si>
@@ -519,6 +519,15 @@
     <t>CASCADE 删除：删除用户时级联删除其菜谱</t>
   </si>
   <si>
+    <t>recipe_id</t>
+  </si>
+  <si>
+    <t>菜品id</t>
+  </si>
+  <si>
+    <t>recipe_name</t>
+  </si>
+  <si>
     <t>用户自定义菜名</t>
   </si>
   <si>
@@ -628,9 +637,6 @@
   </si>
   <si>
     <t>每个版本一个唯一 ID</t>
-  </si>
-  <si>
-    <t>recipe_id</t>
   </si>
   <si>
     <t>所属菜谱 ID</t>
@@ -3130,7 +3136,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -3193,9 +3199,7 @@
       <c r="A8" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="14" t="s">
-        <v>8</v>
-      </c>
+      <c r="B8" s="14"/>
       <c r="C8" s="12" t="s">
         <v>155</v>
       </c>
@@ -3208,192 +3212,186 @@
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:5">
       <c r="A9" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="B9" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="B9" s="13"/>
+      <c r="C9" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+    </row>
+    <row r="10" ht="20" customHeight="1" spans="1:5">
+      <c r="A10" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="B10" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C10" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D10" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E9" s="8" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1" spans="1:5">
-      <c r="A10" s="14" t="s">
-        <v>159</v>
-      </c>
-      <c r="B10" s="14" t="s">
+      <c r="E10" s="8" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1" spans="1:5">
+      <c r="A11" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="B11" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1" spans="1:5">
-      <c r="A11" s="13" t="s">
+      <c r="C11" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="D11" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="E11" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="D11" s="8" t="s">
+    </row>
+    <row r="12" ht="20" customHeight="1" spans="1:5">
+      <c r="A12" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="D12" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="E11" s="8" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1" spans="1:5">
-      <c r="A12" s="14" t="s">
+      <c r="E12" s="8" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1" spans="1:5">
+      <c r="A13" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="B13" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="C12" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="D12" s="12" t="s">
+      <c r="C13" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="D13" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E12" s="12" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1" spans="1:5">
-      <c r="A13" s="13" t="s">
-        <v>169</v>
-      </c>
-      <c r="B13" s="13" t="s">
+      <c r="E13" s="12" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1" spans="1:5">
+      <c r="A14" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="B14" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="14" ht="20" customHeight="1" spans="1:5">
-      <c r="A14" s="14" t="s">
+      <c r="C14" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1" spans="1:5">
+      <c r="A15" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="14" t="s">
+      <c r="B15" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C15" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="D14" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="E14" s="12" t="s">
+      <c r="D15" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="E15" s="12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="15" ht="20" customHeight="1" spans="1:5">
-      <c r="A15" s="13" t="s">
+    <row r="16" ht="20" customHeight="1" spans="1:5">
+      <c r="A16" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B16" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C16" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D16" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="E16" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" ht="20" customHeight="1" spans="1:5">
-      <c r="A16" s="14" t="s">
+    <row r="17" ht="20" customHeight="1" spans="1:5">
+      <c r="A17" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="B16" s="14" t="s">
+      <c r="B17" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C17" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D17" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="E16" s="12" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="19" ht="18" spans="1:5">
-      <c r="A19" s="2" t="s">
+      <c r="E17" s="12" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="20" ht="18" spans="1:5">
+      <c r="A20" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-    </row>
-    <row r="20" ht="16.5" spans="1:5">
-      <c r="A20" s="6" t="s">
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+    </row>
+    <row r="21" ht="16.5" spans="1:5">
+      <c r="A21" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B21" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C21" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="D21" s="6" t="s">
         <v>4</v>
-      </c>
-    </row>
-    <row r="21" ht="16.5" spans="1:5">
-      <c r="A21" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="B21" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="C21" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="D21" s="14" t="s">
-        <v>176</v>
-      </c>
-      <c r="E21" s="17" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:5">
       <c r="A22" s="14" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B22" s="14" t="s">
         <v>64</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>163</v>
+        <v>12</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E22" s="17" t="s">
         <v>11</v>
@@ -3401,16 +3399,16 @@
     </row>
     <row r="23" ht="16.5" spans="1:5">
       <c r="A23" s="14" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B23" s="14" t="s">
         <v>64</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>42</v>
+        <v>166</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E23" s="17" t="s">
         <v>11</v>
@@ -3418,88 +3416,105 @@
     </row>
     <row r="24" ht="16.5" spans="1:5">
       <c r="A24" s="14" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B24" s="14" t="s">
         <v>64</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E24" s="17" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="25" ht="33" spans="1:5">
+    <row r="25" ht="16.5" spans="1:5">
       <c r="A25" s="14" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B25" s="14" t="s">
         <v>64</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>169</v>
+        <v>51</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E25" s="17" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="28" ht="16.5" spans="1:5">
-      <c r="A28" s="18" t="s">
-        <v>185</v>
-      </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
+    <row r="26" ht="33" spans="1:5">
+      <c r="A26" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="E26" s="17" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="29" ht="16.5" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>186</v>
-      </c>
+      <c r="A29" s="18" t="s">
+        <v>188</v>
+      </c>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
     </row>
     <row r="30" ht="16.5" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="31" ht="16.5" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="32" ht="16.5" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="33" ht="16.5" spans="1:1">
       <c r="A33" s="5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="34" ht="16.5" spans="1:1">
       <c r="A34" s="5" t="s">
-        <v>191</v>
+        <v>193</v>
+      </c>
+    </row>
+    <row r="35" ht="16.5" spans="1:1">
+      <c r="A35" s="5" t="s">
+        <v>194</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A20:E20"/>
     <mergeCell ref="A29:E29"/>
     <mergeCell ref="A30:E30"/>
     <mergeCell ref="A31:E31"/>
     <mergeCell ref="A32:E32"/>
     <mergeCell ref="A33:E33"/>
     <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A35:E35"/>
     <mergeCell ref="A1:E2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3522,13 +3537,13 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1"/>
     <row r="5" ht="24" customHeight="1" spans="1:5">
       <c r="A5" s="16" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -3566,41 +3581,41 @@
         <v>10</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:5">
       <c r="A8" s="14" t="s">
-        <v>195</v>
+        <v>158</v>
       </c>
       <c r="B8" s="14" t="s">
         <v>8</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:5">
       <c r="A9" s="13" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B9" s="13" t="s">
         <v>106</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:5">
@@ -3611,13 +3626,13 @@
         <v>85</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D10" s="12" t="s">
         <v>26</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:5">
@@ -3628,64 +3643,64 @@
         <v>85</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>26</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:5">
       <c r="A12" s="14" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B12" s="14" t="s">
         <v>75</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D12" s="12" t="s">
         <v>35</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:5">
       <c r="A13" s="13" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>85</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>35</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:5">
       <c r="A14" s="14" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B14" s="14" t="s">
         <v>13</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D14" s="12" t="s">
         <v>30</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:5">
@@ -3699,10 +3714,10 @@
         <v>44</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:5">
@@ -3730,16 +3745,16 @@
     </row>
     <row r="20" ht="16.5" spans="1:5">
       <c r="A20" s="14" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B20" s="14" t="s">
         <v>59</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E20" s="17" t="s">
         <v>11</v>
@@ -3747,16 +3762,16 @@
     </row>
     <row r="21" ht="33" spans="1:5">
       <c r="A21" s="14" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B21" s="14" t="s">
         <v>64</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>195</v>
+        <v>158</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E21" s="17" t="s">
         <v>11</v>
@@ -3764,7 +3779,7 @@
     </row>
     <row r="22" ht="33" spans="1:5">
       <c r="A22" s="14" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B22" s="14" t="s">
         <v>64</v>
@@ -3773,7 +3788,7 @@
         <v>42</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E22" s="17" t="s">
         <v>11</v>
@@ -3781,7 +3796,7 @@
     </row>
     <row r="25" ht="16.5" spans="1:5">
       <c r="A25" s="18" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -3790,37 +3805,37 @@
     </row>
     <row r="26" ht="16.5" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="27" ht="16.5" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="28" ht="16.5" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="29" ht="16.5" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="30" ht="16.5" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="31" ht="16.5" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="32" ht="16.5" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -3850,13 +3865,13 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1"/>
     <row r="5" ht="18" spans="1:5">
       <c r="A5" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -3865,92 +3880,92 @@
     </row>
     <row r="6" ht="33" spans="1:5">
       <c r="A6" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:5">
       <c r="A7" s="13" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C7" s="13" t="s">
         <v>12</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:5">
       <c r="A8" s="14" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>195</v>
+        <v>158</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:5">
       <c r="A9" s="13" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:5">
       <c r="A10" s="14" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:5">
       <c r="A13" s="2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -3964,107 +3979,107 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="15" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="15" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="15" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="15" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="15" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="15" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="15" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="15" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="15" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="15" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="15" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="15" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="15" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="15" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="15" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="15" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="15" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="15" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="15" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="36" ht="16.5" spans="1:5">
@@ -4074,7 +4089,7 @@
     </row>
     <row r="39" ht="18" spans="1:5">
       <c r="A39" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -4083,92 +4098,92 @@
     </row>
     <row r="40" ht="33" spans="1:5">
       <c r="A40" s="6" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="41" ht="36" customHeight="1" spans="1:5">
       <c r="A41" s="8" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="42" ht="36" customHeight="1" spans="1:5">
       <c r="A42" s="12" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B42" s="12" t="s">
+        <v>285</v>
+      </c>
+      <c r="C42" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="D42" s="12" t="s">
         <v>283</v>
       </c>
-      <c r="C42" s="12" t="s">
+      <c r="E42" s="12" t="s">
         <v>284</v>
-      </c>
-      <c r="D42" s="12" t="s">
-        <v>281</v>
-      </c>
-      <c r="E42" s="12" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="43" ht="36" customHeight="1" spans="1:5">
       <c r="A43" s="8" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="44" ht="36" customHeight="1" spans="1:5">
       <c r="A44" s="12" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C44" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="D44" s="12" t="s">
+        <v>289</v>
+      </c>
+      <c r="E44" s="12" t="s">
         <v>284</v>
-      </c>
-      <c r="D44" s="12" t="s">
-        <v>287</v>
-      </c>
-      <c r="E44" s="12" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="47" ht="18" spans="1:5">
       <c r="A47" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
@@ -4182,167 +4197,167 @@
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="15" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="15" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="15" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="15" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="15" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="15" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="15" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="15" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="15" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="15" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="15" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="15" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="15" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="15" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="15" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="15" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="15" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="15" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="15" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="15" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="15" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="15" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="15" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="15" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="15" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="15" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="15" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="15" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="15" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="15" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="15" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="15" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="15" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="82" spans="1:1">
@@ -4434,12 +4449,12 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:5">
       <c r="A5" s="2" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -4448,57 +4463,57 @@
     </row>
     <row r="6" ht="16.5" spans="1:5">
       <c r="A6" s="4" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="7" ht="40" customHeight="1" spans="1:5">
       <c r="A7" s="5" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:5">
       <c r="A8" s="4" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="9" ht="40" customHeight="1" spans="1:5">
       <c r="A9" s="5" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:5">
       <c r="A10" s="4" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="11" ht="40" customHeight="1" spans="1:5">
       <c r="A11" s="5" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:5">
       <c r="A12" s="4" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="13" ht="40" customHeight="1" spans="1:5">
       <c r="A13" s="5" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:5">
       <c r="A14" s="4" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="15" ht="40" customHeight="1" spans="1:5">
       <c r="A15" s="5" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:5">
       <c r="A18" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -4507,77 +4522,77 @@
     </row>
     <row r="19" ht="16.5" spans="1:5">
       <c r="A19" s="4" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="20" ht="50" customHeight="1" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:5">
       <c r="A21" s="4" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="22" ht="50" customHeight="1" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:5">
       <c r="A23" s="4" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="24" ht="50" customHeight="1" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="25" ht="16.5" spans="1:5">
       <c r="A25" s="4" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="26" ht="50" customHeight="1" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="27" ht="16.5" spans="1:5">
       <c r="A27" s="4" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="28" ht="50" customHeight="1" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="29" ht="16.5" spans="1:5">
       <c r="A29" s="4" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="30" ht="50" customHeight="1" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="31" ht="16.5" spans="1:5">
       <c r="A31" s="4" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="32" ht="50" customHeight="1" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="35" ht="18" spans="1:5">
       <c r="A35" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -4586,81 +4601,81 @@
     </row>
     <row r="36" ht="16.5" spans="1:5">
       <c r="A36" s="6" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="37" ht="36" customHeight="1" spans="1:5">
       <c r="A37" s="7" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="10"/>
     </row>
     <row r="38" ht="36" customHeight="1" spans="1:5">
       <c r="A38" s="11" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C38" s="9"/>
       <c r="D38" s="10"/>
     </row>
     <row r="39" ht="36" customHeight="1" spans="1:5">
       <c r="A39" s="7" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="10"/>
     </row>
     <row r="40" ht="36" customHeight="1" spans="1:5">
       <c r="A40" s="11" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C40" s="9"/>
       <c r="D40" s="10"/>
     </row>
     <row r="41" ht="36" customHeight="1" spans="1:5">
       <c r="A41" s="7" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="10"/>
     </row>
     <row r="42" ht="36" customHeight="1" spans="1:5">
       <c r="A42" s="11" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C42" s="9"/>
       <c r="D42" s="10"/>
     </row>
     <row r="43" ht="36" customHeight="1" spans="1:5">
       <c r="A43" s="7" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="10"/>

--- a/docs/database/人间烟火_数据库设计文档.xlsx
+++ b/docs/database/人间烟火_数据库设计文档.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="18360" activeTab="2"/>
+    <workbookView windowHeight="18360" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="用户管理" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="354">
   <si>
     <t>用户管理</t>
   </si>
@@ -546,7 +546,7 @@
     <t>user_rating</t>
   </si>
   <si>
-    <t>TINYINT UNSIGNED</t>
+    <t xml:space="preserve">TINYINT </t>
   </si>
   <si>
     <t>个人评分 1-5 星</t>
@@ -609,27 +609,6 @@
     <t>关联百科菜谱查询</t>
   </si>
   <si>
-    <t>▶ 版本控制写入流程（应用层事务）</t>
-  </si>
-  <si>
-    <t>1. 新建菜谱: INSERT my_recipes (current_version_id = NULL)</t>
-  </si>
-  <si>
-    <t>2. 创建首个版本: INSERT recipe_versions (version_number = 1)</t>
-  </si>
-  <si>
-    <t>3. 回填版本指针: UPDATE my_recipes SET current_version_id = 新版本.id</t>
-  </si>
-  <si>
-    <t>4. 编辑菜谱: INSERT recipe_versions (version_number = MAX(version_number) + 1)</t>
-  </si>
-  <si>
-    <t>5. 更新指针: UPDATE my_recipes SET current_version_id = 新版本.id</t>
-  </si>
-  <si>
-    <t>★ 核心原则: 编辑时仅 INSERT 新版本行，绝不 UPDATE 旧版本行（不可变记录）</t>
-  </si>
-  <si>
     <t>版本管理</t>
   </si>
   <si>
@@ -648,9 +627,18 @@
     <t>CASCADE 删除：删除菜谱时级联删除所有版本</t>
   </si>
   <si>
+    <t>recipe_version_id</t>
+  </si>
+  <si>
+    <t>菜品版本号id</t>
+  </si>
+  <si>
     <t>version_number</t>
   </si>
   <si>
+    <t>INT</t>
+  </si>
+  <si>
     <t>版本号</t>
   </si>
   <si>
@@ -700,27 +688,6 @@
   </si>
   <si>
     <t>版本创建时间（不可变）</t>
-  </si>
-  <si>
-    <t>uk_recipe_version</t>
-  </si>
-  <si>
-    <t>(recipe_id, version_number)</t>
-  </si>
-  <si>
-    <t>保证同一菜谱下版本号唯一</t>
-  </si>
-  <si>
-    <t>idx_recipe_versions_recipe_id</t>
-  </si>
-  <si>
-    <t>加速按菜谱查询所有版本</t>
-  </si>
-  <si>
-    <t>idx_recipe_versions_created_at</t>
-  </si>
-  <si>
-    <t>加速按时间排序</t>
   </si>
   <si>
     <t>▶ 版本对比算法（diff 包）</t>
@@ -1904,8 +1871,8 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2517,7 +2484,7 @@
       <c r="D22" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="E22" s="17" t="s">
+      <c r="E22" s="18" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2534,7 +2501,7 @@
       <c r="D23" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="E23" s="17" t="s">
+      <c r="E23" s="18" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2551,7 +2518,7 @@
       <c r="D24" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="E24" s="17" t="s">
+      <c r="E24" s="18" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2898,7 +2865,7 @@
       <c r="D26" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="E26" s="17" t="s">
+      <c r="E26" s="18" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2915,7 +2882,7 @@
       <c r="D27" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="E27" s="17" t="s">
+      <c r="E27" s="18" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2932,7 +2899,7 @@
       <c r="D28" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="E28" s="17" t="s">
+      <c r="E28" s="18" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2949,7 +2916,7 @@
       <c r="D29" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="E29" s="17" t="s">
+      <c r="E29" s="18" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3136,7 +3103,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -3393,7 +3360,7 @@
       <c r="D22" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="E22" s="17" t="s">
+      <c r="E22" s="18" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3410,7 +3377,7 @@
       <c r="D23" s="14" t="s">
         <v>181</v>
       </c>
-      <c r="E23" s="17" t="s">
+      <c r="E23" s="18" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3427,7 +3394,7 @@
       <c r="D24" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="E24" s="17" t="s">
+      <c r="E24" s="18" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3444,7 +3411,7 @@
       <c r="D25" s="14" t="s">
         <v>185</v>
       </c>
-      <c r="E25" s="17" t="s">
+      <c r="E25" s="18" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3461,60 +3428,14 @@
       <c r="D26" s="14" t="s">
         <v>187</v>
       </c>
-      <c r="E26" s="17" t="s">
+      <c r="E26" s="18" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="29" ht="16.5" spans="1:5">
-      <c r="A29" s="18" t="s">
-        <v>188</v>
-      </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
-    </row>
-    <row r="30" ht="16.5" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="31" ht="16.5" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="32" ht="16.5" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="33" ht="16.5" spans="1:1">
-      <c r="A33" s="5" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="34" ht="16.5" spans="1:1">
-      <c r="A34" s="5" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="35" ht="16.5" spans="1:1">
-      <c r="A35" s="5" t="s">
-        <v>194</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="3">
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A29:E29"/>
-    <mergeCell ref="A30:E30"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="A32:E32"/>
-    <mergeCell ref="A33:E33"/>
-    <mergeCell ref="A34:E34"/>
-    <mergeCell ref="A35:E35"/>
     <mergeCell ref="A1:E2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3525,7 +3446,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -3537,13 +3458,13 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1"/>
     <row r="5" ht="24" customHeight="1" spans="1:5">
       <c r="A5" s="16" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -3581,275 +3502,209 @@
         <v>10</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:5">
       <c r="A8" s="14" t="s">
         <v>158</v>
       </c>
-      <c r="B8" s="14" t="s">
-        <v>8</v>
-      </c>
+      <c r="B8" s="14"/>
       <c r="C8" s="12" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:5">
       <c r="A9" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="B9" s="13"/>
+      <c r="C9" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+    </row>
+    <row r="10" ht="20" customHeight="1" spans="1:5">
+      <c r="A10" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1" spans="1:5">
+      <c r="A11" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="C11" s="12" t="s">
         <v>201</v>
       </c>
-      <c r="B9" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="C9" s="8" t="s">
+      <c r="D11" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="12" t="s">
         <v>202</v>
       </c>
-      <c r="D9" s="8" t="s">
+    </row>
+    <row r="12" ht="20" customHeight="1" spans="1:5">
+      <c r="A12" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="D12" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" s="8" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="10" ht="20" customHeight="1" spans="1:5">
-      <c r="A10" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="B10" s="14" t="s">
+    <row r="13" ht="20" customHeight="1" spans="1:5">
+      <c r="A13" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1" spans="1:5">
+      <c r="A14" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="B14" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="C10" s="12" t="s">
-        <v>205</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1" spans="1:5">
-      <c r="A11" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1" spans="1:5">
-      <c r="A12" s="14" t="s">
+      <c r="C14" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="B12" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="C12" s="12" t="s">
+      <c r="D14" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="D12" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E12" s="12" t="s">
+    </row>
+    <row r="15" ht="20" customHeight="1" spans="1:5">
+      <c r="A15" s="14" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="13" ht="20" customHeight="1" spans="1:5">
-      <c r="A13" s="13" t="s">
+      <c r="B15" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" s="12" t="s">
         <v>212</v>
       </c>
-      <c r="B13" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="C13" s="8" t="s">
+      <c r="D15" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" s="12" t="s">
         <v>213</v>
       </c>
-      <c r="D13" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E13" s="8" t="s">
+    </row>
+    <row r="16" ht="20" customHeight="1" spans="1:5">
+      <c r="A16" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="E16" s="8" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="14" ht="20" customHeight="1" spans="1:5">
-      <c r="A14" s="14" t="s">
+    <row r="21" ht="16.5" spans="1:5">
+      <c r="A21" s="17" t="s">
         <v>215</v>
       </c>
-      <c r="B14" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14" s="12" t="s">
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+    </row>
+    <row r="22" ht="16.5" spans="1:5">
+      <c r="A22" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="D14" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="E14" s="12" t="s">
+    </row>
+    <row r="23" ht="16.5" spans="1:5">
+      <c r="A23" s="5" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="15" ht="20" customHeight="1" spans="1:5">
-      <c r="A15" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="E15" s="8" t="s">
+    <row r="24" ht="16.5" spans="1:5">
+      <c r="A24" s="5" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="18" ht="18" spans="1:5">
-      <c r="A18" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-    </row>
-    <row r="19" ht="16.5" spans="1:5">
-      <c r="A19" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20" ht="16.5" spans="1:5">
-      <c r="A20" s="14" t="s">
+    <row r="25" ht="16.5" spans="1:5">
+      <c r="A25" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="B20" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C20" s="14" t="s">
-        <v>220</v>
-      </c>
-      <c r="D20" s="14" t="s">
-        <v>221</v>
-      </c>
-      <c r="E20" s="17" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" ht="33" spans="1:5">
-      <c r="A21" s="14" t="s">
-        <v>222</v>
-      </c>
-      <c r="B21" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="C21" s="14" t="s">
-        <v>158</v>
-      </c>
-      <c r="D21" s="14" t="s">
-        <v>223</v>
-      </c>
-      <c r="E21" s="17" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" ht="33" spans="1:5">
-      <c r="A22" s="14" t="s">
-        <v>224</v>
-      </c>
-      <c r="B22" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="C22" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="D22" s="14" t="s">
-        <v>225</v>
-      </c>
-      <c r="E22" s="17" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="25" ht="16.5" spans="1:5">
-      <c r="A25" s="18" t="s">
-        <v>226</v>
-      </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
     </row>
     <row r="26" ht="16.5" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
     </row>
     <row r="27" ht="16.5" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
     </row>
     <row r="28" ht="16.5" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="29" ht="16.5" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="30" ht="16.5" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="31" ht="16.5" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="32" ht="16.5" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A24:E24"/>
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="A26:E26"/>
     <mergeCell ref="A27:E27"/>
     <mergeCell ref="A28:E28"/>
-    <mergeCell ref="A29:E29"/>
-    <mergeCell ref="A30:E30"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="A32:E32"/>
     <mergeCell ref="A1:E2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3865,13 +3720,13 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1"/>
     <row r="5" ht="18" spans="1:5">
       <c r="A5" s="2" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -3880,92 +3735,92 @@
     </row>
     <row r="6" ht="33" spans="1:5">
       <c r="A6" s="6" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:5">
       <c r="A7" s="13" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="C7" s="13" t="s">
         <v>12</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:5">
       <c r="A8" s="14" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="C8" s="14" t="s">
         <v>158</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:5">
       <c r="A9" s="13" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="C9" s="13" t="s">
         <v>162</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:5">
       <c r="A10" s="14" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="C10" s="14" t="s">
         <v>172</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:5">
       <c r="A13" s="2" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -3979,107 +3834,107 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="15" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="15" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="15" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="15" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="15" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="15" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="15" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="15" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="15" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="15" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="15" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="15" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="15" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="15" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="15" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="15" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="15" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="15" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="15" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="15" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="15" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
     </row>
     <row r="36" ht="16.5" spans="1:5">
@@ -4089,7 +3944,7 @@
     </row>
     <row r="39" ht="18" spans="1:5">
       <c r="A39" s="2" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -4098,92 +3953,92 @@
     </row>
     <row r="40" ht="33" spans="1:5">
       <c r="A40" s="6" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
     </row>
     <row r="41" ht="36" customHeight="1" spans="1:5">
       <c r="A41" s="8" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
     </row>
     <row r="42" ht="36" customHeight="1" spans="1:5">
       <c r="A42" s="12" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
     </row>
     <row r="43" ht="36" customHeight="1" spans="1:5">
       <c r="A43" s="8" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>288</v>
+        <v>277</v>
       </c>
     </row>
     <row r="44" ht="36" customHeight="1" spans="1:5">
       <c r="A44" s="12" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
     </row>
     <row r="47" ht="18" spans="1:5">
       <c r="A47" s="2" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
@@ -4197,167 +4052,167 @@
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="15" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="15" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="15" t="s">
-        <v>293</v>
+        <v>282</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="15" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="15" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="15" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="15" t="s">
-        <v>297</v>
+        <v>286</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="15" t="s">
-        <v>298</v>
+        <v>287</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="15" t="s">
-        <v>299</v>
+        <v>288</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="15" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="15" t="s">
-        <v>301</v>
+        <v>290</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="15" t="s">
-        <v>302</v>
+        <v>291</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="15" t="s">
-        <v>303</v>
+        <v>292</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="15" t="s">
-        <v>304</v>
+        <v>293</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="15" t="s">
-        <v>305</v>
+        <v>294</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="15" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="15" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="15" t="s">
-        <v>307</v>
+        <v>296</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="15" t="s">
-        <v>308</v>
+        <v>297</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="15" t="s">
-        <v>309</v>
+        <v>298</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="15" t="s">
-        <v>310</v>
+        <v>299</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="15" t="s">
-        <v>311</v>
+        <v>300</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="15" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="15" t="s">
-        <v>312</v>
+        <v>301</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="15" t="s">
-        <v>313</v>
+        <v>302</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="15" t="s">
-        <v>314</v>
+        <v>303</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="15" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="15" t="s">
-        <v>315</v>
+        <v>304</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="15" t="s">
-        <v>316</v>
+        <v>305</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="15" t="s">
-        <v>317</v>
+        <v>306</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="15" t="s">
-        <v>318</v>
+        <v>307</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="15" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="15" t="s">
-        <v>319</v>
+        <v>308</v>
       </c>
     </row>
     <row r="82" spans="1:1">
@@ -4449,12 +4304,12 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:5">
       <c r="A5" s="2" t="s">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -4463,57 +4318,57 @@
     </row>
     <row r="6" ht="16.5" spans="1:5">
       <c r="A6" s="4" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
     </row>
     <row r="7" ht="40" customHeight="1" spans="1:5">
       <c r="A7" s="5" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:5">
       <c r="A8" s="4" t="s">
-        <v>324</v>
+        <v>313</v>
       </c>
     </row>
     <row r="9" ht="40" customHeight="1" spans="1:5">
       <c r="A9" s="5" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:5">
       <c r="A10" s="4" t="s">
-        <v>326</v>
+        <v>315</v>
       </c>
     </row>
     <row r="11" ht="40" customHeight="1" spans="1:5">
       <c r="A11" s="5" t="s">
-        <v>327</v>
+        <v>316</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:5">
       <c r="A12" s="4" t="s">
-        <v>328</v>
+        <v>317</v>
       </c>
     </row>
     <row r="13" ht="40" customHeight="1" spans="1:5">
       <c r="A13" s="5" t="s">
-        <v>329</v>
+        <v>318</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:5">
       <c r="A14" s="4" t="s">
-        <v>330</v>
+        <v>319</v>
       </c>
     </row>
     <row r="15" ht="40" customHeight="1" spans="1:5">
       <c r="A15" s="5" t="s">
-        <v>331</v>
+        <v>320</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:5">
       <c r="A18" s="2" t="s">
-        <v>332</v>
+        <v>321</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -4522,77 +4377,77 @@
     </row>
     <row r="19" ht="16.5" spans="1:5">
       <c r="A19" s="4" t="s">
-        <v>333</v>
+        <v>322</v>
       </c>
     </row>
     <row r="20" ht="50" customHeight="1" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:5">
       <c r="A21" s="4" t="s">
-        <v>335</v>
+        <v>324</v>
       </c>
     </row>
     <row r="22" ht="50" customHeight="1" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>336</v>
+        <v>325</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:5">
       <c r="A23" s="4" t="s">
-        <v>337</v>
+        <v>326</v>
       </c>
     </row>
     <row r="24" ht="50" customHeight="1" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>338</v>
+        <v>327</v>
       </c>
     </row>
     <row r="25" ht="16.5" spans="1:5">
       <c r="A25" s="4" t="s">
-        <v>339</v>
+        <v>328</v>
       </c>
     </row>
     <row r="26" ht="50" customHeight="1" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>340</v>
+        <v>329</v>
       </c>
     </row>
     <row r="27" ht="16.5" spans="1:5">
       <c r="A27" s="4" t="s">
-        <v>341</v>
+        <v>330</v>
       </c>
     </row>
     <row r="28" ht="50" customHeight="1" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>342</v>
+        <v>331</v>
       </c>
     </row>
     <row r="29" ht="16.5" spans="1:5">
       <c r="A29" s="4" t="s">
-        <v>343</v>
+        <v>332</v>
       </c>
     </row>
     <row r="30" ht="50" customHeight="1" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>344</v>
+        <v>333</v>
       </c>
     </row>
     <row r="31" ht="16.5" spans="1:5">
       <c r="A31" s="4" t="s">
-        <v>345</v>
+        <v>334</v>
       </c>
     </row>
     <row r="32" ht="50" customHeight="1" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>346</v>
+        <v>335</v>
       </c>
     </row>
     <row r="35" ht="18" spans="1:5">
       <c r="A35" s="2" t="s">
-        <v>347</v>
+        <v>336</v>
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -4601,81 +4456,81 @@
     </row>
     <row r="36" ht="16.5" spans="1:5">
       <c r="A36" s="6" t="s">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>349</v>
+        <v>338</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>350</v>
+        <v>339</v>
       </c>
     </row>
     <row r="37" ht="36" customHeight="1" spans="1:5">
       <c r="A37" s="7" t="s">
-        <v>351</v>
+        <v>340</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>352</v>
+        <v>341</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="10"/>
     </row>
     <row r="38" ht="36" customHeight="1" spans="1:5">
       <c r="A38" s="11" t="s">
-        <v>353</v>
+        <v>342</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>354</v>
+        <v>343</v>
       </c>
       <c r="C38" s="9"/>
       <c r="D38" s="10"/>
     </row>
     <row r="39" ht="36" customHeight="1" spans="1:5">
       <c r="A39" s="7" t="s">
-        <v>355</v>
+        <v>344</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>356</v>
+        <v>345</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="10"/>
     </row>
     <row r="40" ht="36" customHeight="1" spans="1:5">
       <c r="A40" s="11" t="s">
-        <v>357</v>
+        <v>346</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>358</v>
+        <v>347</v>
       </c>
       <c r="C40" s="9"/>
       <c r="D40" s="10"/>
     </row>
     <row r="41" ht="36" customHeight="1" spans="1:5">
       <c r="A41" s="7" t="s">
-        <v>359</v>
+        <v>348</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>360</v>
+        <v>349</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="10"/>
     </row>
     <row r="42" ht="36" customHeight="1" spans="1:5">
       <c r="A42" s="11" t="s">
-        <v>361</v>
+        <v>350</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>362</v>
+        <v>351</v>
       </c>
       <c r="C42" s="9"/>
       <c r="D42" s="10"/>
     </row>
     <row r="43" ht="36" customHeight="1" spans="1:5">
       <c r="A43" s="7" t="s">
-        <v>363</v>
+        <v>352</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="10"/>

--- a/docs/database/人间烟火_数据库设计文档.xlsx
+++ b/docs/database/人间烟火_数据库设计文档.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="18360" activeTab="3"/>
+    <workbookView windowHeight="18360" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="用户管理" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="353">
   <si>
     <t>用户管理</t>
   </si>
@@ -352,7 +352,7 @@
     <t>view_count</t>
   </si>
   <si>
-    <t>INT UNSIGNED</t>
+    <t>INT</t>
   </si>
   <si>
     <t>浏览次数</t>
@@ -634,9 +634,6 @@
   </si>
   <si>
     <t>version_number</t>
-  </si>
-  <si>
-    <t>INT</t>
   </si>
   <si>
     <t>版本号</t>
@@ -3536,16 +3533,16 @@
         <v>196</v>
       </c>
       <c r="B10" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="C10" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="D10" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="E10" s="8" t="s">
         <v>199</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:5">
@@ -3556,13 +3553,13 @@
         <v>85</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D11" s="12" t="s">
         <v>26</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:5">
@@ -3573,64 +3570,64 @@
         <v>85</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>26</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:5">
       <c r="A13" s="14" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B13" s="14" t="s">
         <v>75</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D13" s="12" t="s">
         <v>35</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:5">
       <c r="A14" s="13" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B14" s="13" t="s">
         <v>85</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>35</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:5">
       <c r="A15" s="14" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B15" s="14" t="s">
         <v>13</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D15" s="12" t="s">
         <v>30</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:5">
@@ -3647,12 +3644,12 @@
         <v>176</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:5">
       <c r="A21" s="17" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -3661,37 +3658,37 @@
     </row>
     <row r="22" ht="16.5" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="25" ht="16.5" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="26" ht="16.5" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="27" ht="16.5" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="28" ht="16.5" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -3720,13 +3717,13 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1"/>
     <row r="5" ht="18" spans="1:5">
       <c r="A5" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -3735,92 +3732,92 @@
     </row>
     <row r="6" ht="33" spans="1:5">
       <c r="A6" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="C6" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="E6" s="6" t="s">
         <v>228</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:5">
       <c r="A7" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="B7" s="13" t="s">
         <v>230</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>231</v>
       </c>
       <c r="C7" s="13" t="s">
         <v>12</v>
       </c>
       <c r="D7" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="E7" s="13" t="s">
         <v>232</v>
-      </c>
-      <c r="E7" s="13" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:5">
       <c r="A8" s="14" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C8" s="14" t="s">
         <v>158</v>
       </c>
       <c r="D8" s="14" t="s">
+        <v>234</v>
+      </c>
+      <c r="E8" s="14" t="s">
         <v>235</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:5">
       <c r="A9" s="13" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C9" s="13" t="s">
         <v>162</v>
       </c>
       <c r="D9" s="13" t="s">
+        <v>236</v>
+      </c>
+      <c r="E9" s="13" t="s">
         <v>237</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:5">
       <c r="A10" s="14" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C10" s="14" t="s">
         <v>172</v>
       </c>
       <c r="D10" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="E10" s="14" t="s">
         <v>240</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:5">
       <c r="A13" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -3834,107 +3831,107 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="15" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="15" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="15" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="15" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="15" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="15" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="15" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="15" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="15" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="15" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="15" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="15" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="15" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="15" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="15" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="15" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="15" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="15" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="15" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="15" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="36" ht="16.5" spans="1:5">
@@ -3944,7 +3941,7 @@
     </row>
     <row r="39" ht="18" spans="1:5">
       <c r="A39" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -3953,92 +3950,92 @@
     </row>
     <row r="40" ht="33" spans="1:5">
       <c r="A40" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="B40" s="6" t="s">
         <v>265</v>
       </c>
-      <c r="B40" s="6" t="s">
+      <c r="C40" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="C40" s="6" t="s">
+      <c r="D40" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="D40" s="6" t="s">
+      <c r="E40" s="6" t="s">
         <v>268</v>
-      </c>
-      <c r="E40" s="6" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="41" ht="36" customHeight="1" spans="1:5">
       <c r="A41" s="8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B41" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="C41" s="8" t="s">
         <v>270</v>
       </c>
-      <c r="C41" s="8" t="s">
+      <c r="D41" s="8" t="s">
         <v>271</v>
       </c>
-      <c r="D41" s="8" t="s">
+      <c r="E41" s="8" t="s">
         <v>272</v>
-      </c>
-      <c r="E41" s="8" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="42" ht="36" customHeight="1" spans="1:5">
       <c r="A42" s="12" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B42" s="12" t="s">
+        <v>273</v>
+      </c>
+      <c r="C42" s="12" t="s">
         <v>274</v>
       </c>
-      <c r="C42" s="12" t="s">
-        <v>275</v>
-      </c>
       <c r="D42" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="E42" s="12" t="s">
         <v>272</v>
-      </c>
-      <c r="E42" s="12" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="43" ht="36" customHeight="1" spans="1:5">
       <c r="A43" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C43" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="D43" s="8" t="s">
         <v>275</v>
       </c>
-      <c r="D43" s="8" t="s">
+      <c r="E43" s="8" t="s">
         <v>276</v>
-      </c>
-      <c r="E43" s="8" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="44" ht="36" customHeight="1" spans="1:5">
       <c r="A44" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="47" ht="18" spans="1:5">
       <c r="A47" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
@@ -4052,167 +4049,167 @@
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="15" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="15" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="15" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="15" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="15" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="15" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="15" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="15" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="15" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="15" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="15" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="15" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="15" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="15" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="15" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="15" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="15" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="15" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="15" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="15" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="15" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="15" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="15" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="15" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="15" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="15" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="15" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="15" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="15" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="15" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="15" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="82" spans="1:1">
@@ -4304,12 +4301,12 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:5">
       <c r="A5" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -4318,57 +4315,57 @@
     </row>
     <row r="6" ht="16.5" spans="1:5">
       <c r="A6" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="7" ht="40" customHeight="1" spans="1:5">
       <c r="A7" s="5" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:5">
       <c r="A8" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="9" ht="40" customHeight="1" spans="1:5">
       <c r="A9" s="5" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:5">
       <c r="A10" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11" ht="40" customHeight="1" spans="1:5">
       <c r="A11" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:5">
       <c r="A12" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="13" ht="40" customHeight="1" spans="1:5">
       <c r="A13" s="5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:5">
       <c r="A14" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="15" ht="40" customHeight="1" spans="1:5">
       <c r="A15" s="5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:5">
       <c r="A18" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -4377,77 +4374,77 @@
     </row>
     <row r="19" ht="16.5" spans="1:5">
       <c r="A19" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="20" ht="50" customHeight="1" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:5">
       <c r="A21" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="22" ht="50" customHeight="1" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:5">
       <c r="A23" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="24" ht="50" customHeight="1" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="25" ht="16.5" spans="1:5">
       <c r="A25" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="26" ht="50" customHeight="1" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="27" ht="16.5" spans="1:5">
       <c r="A27" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="28" ht="50" customHeight="1" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="29" ht="16.5" spans="1:5">
       <c r="A29" s="4" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="30" ht="50" customHeight="1" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="31" ht="16.5" spans="1:5">
       <c r="A31" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="32" ht="50" customHeight="1" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="35" ht="18" spans="1:5">
       <c r="A35" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -4456,81 +4453,81 @@
     </row>
     <row r="36" ht="16.5" spans="1:5">
       <c r="A36" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="B36" s="6" t="s">
         <v>337</v>
       </c>
-      <c r="B36" s="6" t="s">
+      <c r="C36" s="6" t="s">
         <v>338</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="37" ht="36" customHeight="1" spans="1:5">
       <c r="A37" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="B37" s="8" t="s">
         <v>340</v>
-      </c>
-      <c r="B37" s="8" t="s">
-        <v>341</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="10"/>
     </row>
     <row r="38" ht="36" customHeight="1" spans="1:5">
       <c r="A38" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="B38" s="12" t="s">
         <v>342</v>
-      </c>
-      <c r="B38" s="12" t="s">
-        <v>343</v>
       </c>
       <c r="C38" s="9"/>
       <c r="D38" s="10"/>
     </row>
     <row r="39" ht="36" customHeight="1" spans="1:5">
       <c r="A39" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="B39" s="8" t="s">
         <v>344</v>
-      </c>
-      <c r="B39" s="8" t="s">
-        <v>345</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="10"/>
     </row>
     <row r="40" ht="36" customHeight="1" spans="1:5">
       <c r="A40" s="11" t="s">
+        <v>345</v>
+      </c>
+      <c r="B40" s="12" t="s">
         <v>346</v>
-      </c>
-      <c r="B40" s="12" t="s">
-        <v>347</v>
       </c>
       <c r="C40" s="9"/>
       <c r="D40" s="10"/>
     </row>
     <row r="41" ht="36" customHeight="1" spans="1:5">
       <c r="A41" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="B41" s="8" t="s">
         <v>348</v>
-      </c>
-      <c r="B41" s="8" t="s">
-        <v>349</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="10"/>
     </row>
     <row r="42" ht="36" customHeight="1" spans="1:5">
       <c r="A42" s="11" t="s">
+        <v>349</v>
+      </c>
+      <c r="B42" s="12" t="s">
         <v>350</v>
-      </c>
-      <c r="B42" s="12" t="s">
-        <v>351</v>
       </c>
       <c r="C42" s="9"/>
       <c r="D42" s="10"/>
     </row>
     <row r="43" ht="36" customHeight="1" spans="1:5">
       <c r="A43" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="B43" s="8" t="s">
         <v>352</v>
-      </c>
-      <c r="B43" s="8" t="s">
-        <v>353</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="10"/>

--- a/docs/database/人间烟火_数据库设计文档.xlsx
+++ b/docs/database/人间烟火_数据库设计文档.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="354">
   <si>
     <t>用户管理</t>
   </si>
@@ -244,127 +244,130 @@
     <t>百科菜谱id</t>
   </si>
   <si>
+    <t>encyclopedia_recipes_name</t>
+  </si>
+  <si>
+    <t>菜名</t>
+  </si>
+  <si>
+    <t>NOT NULL, INDEX</t>
+  </si>
+  <si>
+    <t>如"红烧肉"、"Kung Pao Chicken"</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>TEXT</t>
+  </si>
+  <si>
+    <t>简介/描述</t>
+  </si>
+  <si>
+    <t>菜品的简要介绍</t>
+  </si>
+  <si>
+    <t>cover_image_url</t>
+  </si>
+  <si>
+    <t>封面图 URL</t>
+  </si>
+  <si>
+    <t>菜品展示图片</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>分类</t>
+  </si>
+  <si>
+    <t>如"家常菜"、"粤菜"、"川菜"、"西餐"等</t>
+  </si>
+  <si>
+    <t>tags</t>
+  </si>
+  <si>
+    <t>JSON</t>
+  </si>
+  <si>
+    <t>标签数组</t>
+  </si>
+  <si>
+    <t>存储格式: ["快手菜","下饭菜","硬菜"]</t>
+  </si>
+  <si>
+    <t>ingredients</t>
+  </si>
+  <si>
+    <t>标准配料与重量</t>
+  </si>
+  <si>
+    <t>存储格式: [{"name":"五花肉","amount":500,"unit":"g","note":"切块"}]</t>
+  </si>
+  <si>
+    <t>process_steps</t>
+  </si>
+  <si>
+    <t>标准制作步骤</t>
+  </si>
+  <si>
+    <t>存储格式: [{"order":1,"content":"焯水...","duration_minutes":5}]</t>
+  </si>
+  <si>
+    <t>source</t>
+  </si>
+  <si>
+    <t>数据来源</t>
+  </si>
+  <si>
+    <t>如"百科"、"spoonacular"、"themealdb"</t>
+  </si>
+  <si>
+    <t>external_source</t>
+  </si>
+  <si>
+    <t>VARCHAR(32)</t>
+  </si>
+  <si>
+    <t>外部来源标识</t>
+  </si>
+  <si>
+    <t>UNIQUE(组合), DEFAULT NULL</t>
+  </si>
+  <si>
+    <t>如"spoonacular"、"themealdb"，用于去重</t>
+  </si>
+  <si>
+    <t>external_id</t>
+  </si>
+  <si>
+    <t>外部 ID</t>
+  </si>
+  <si>
+    <t>在外部源中的唯一标识</t>
+  </si>
+  <si>
+    <t>view_count</t>
+  </si>
+  <si>
+    <t>INT</t>
+  </si>
+  <si>
+    <t>浏览次数</t>
+  </si>
+  <si>
+    <t>NOT NULL, DEFAULT 0</t>
+  </si>
+  <si>
+    <t>每次获取详情时自动 +1,用于做推荐算法</t>
+  </si>
+  <si>
+    <t>idx_encyclopedia_name</t>
+  </si>
+  <si>
     <t>name</t>
-  </si>
-  <si>
-    <t>菜名</t>
-  </si>
-  <si>
-    <t>NOT NULL, INDEX</t>
-  </si>
-  <si>
-    <t>如"红烧肉"、"Kung Pao Chicken"</t>
-  </si>
-  <si>
-    <t>description</t>
-  </si>
-  <si>
-    <t>TEXT</t>
-  </si>
-  <si>
-    <t>简介/描述</t>
-  </si>
-  <si>
-    <t>菜品的简要介绍</t>
-  </si>
-  <si>
-    <t>cover_image_url</t>
-  </si>
-  <si>
-    <t>封面图 URL</t>
-  </si>
-  <si>
-    <t>菜品展示图片</t>
-  </si>
-  <si>
-    <t>category</t>
-  </si>
-  <si>
-    <t>分类</t>
-  </si>
-  <si>
-    <t>如"家常菜"、"粤菜"、"川菜"、"西餐"等</t>
-  </si>
-  <si>
-    <t>tags</t>
-  </si>
-  <si>
-    <t>JSON</t>
-  </si>
-  <si>
-    <t>标签数组</t>
-  </si>
-  <si>
-    <t>存储格式: ["快手菜","下饭菜","硬菜"]</t>
-  </si>
-  <si>
-    <t>ingredients</t>
-  </si>
-  <si>
-    <t>标准配料与重量</t>
-  </si>
-  <si>
-    <t>存储格式: [{"name":"五花肉","amount":500,"unit":"g","note":"切块"}]</t>
-  </si>
-  <si>
-    <t>process_steps</t>
-  </si>
-  <si>
-    <t>标准制作步骤</t>
-  </si>
-  <si>
-    <t>存储格式: [{"order":1,"content":"焯水...","duration_minutes":5}]</t>
-  </si>
-  <si>
-    <t>source</t>
-  </si>
-  <si>
-    <t>数据来源</t>
-  </si>
-  <si>
-    <t>如"百科"、"spoonacular"、"themealdb"</t>
-  </si>
-  <si>
-    <t>external_source</t>
-  </si>
-  <si>
-    <t>VARCHAR(32)</t>
-  </si>
-  <si>
-    <t>外部来源标识</t>
-  </si>
-  <si>
-    <t>UNIQUE(组合), DEFAULT NULL</t>
-  </si>
-  <si>
-    <t>如"spoonacular"、"themealdb"，用于去重</t>
-  </si>
-  <si>
-    <t>external_id</t>
-  </si>
-  <si>
-    <t>外部 ID</t>
-  </si>
-  <si>
-    <t>在外部源中的唯一标识</t>
-  </si>
-  <si>
-    <t>view_count</t>
-  </si>
-  <si>
-    <t>INT</t>
-  </si>
-  <si>
-    <t>浏览次数</t>
-  </si>
-  <si>
-    <t>NOT NULL, DEFAULT 0</t>
-  </si>
-  <si>
-    <t>每次获取详情时自动 +1,用于做推荐算法</t>
-  </si>
-  <si>
-    <t>idx_encyclopedia_name</t>
   </si>
   <si>
     <t>加速按菜名搜索</t>
@@ -2857,10 +2860,10 @@
         <v>64</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>70</v>
+        <v>111</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E26" s="18" t="s">
         <v>11</v>
@@ -2868,7 +2871,7 @@
     </row>
     <row r="27" ht="16.5" spans="1:5">
       <c r="A27" s="14" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B27" s="14" t="s">
         <v>64</v>
@@ -2877,7 +2880,7 @@
         <v>81</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E27" s="18" t="s">
         <v>11</v>
@@ -2885,16 +2888,16 @@
     </row>
     <row r="28" ht="16.5" spans="1:5">
       <c r="A28" s="14" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B28" s="14" t="s">
         <v>59</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E28" s="18" t="s">
         <v>11</v>
@@ -2902,16 +2905,16 @@
     </row>
     <row r="29" ht="16.5" spans="1:5">
       <c r="A29" s="14" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B29" s="14" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E29" s="18" t="s">
         <v>11</v>
@@ -2919,7 +2922,7 @@
     </row>
     <row r="32" ht="18" spans="1:5">
       <c r="A32" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -2928,12 +2931,12 @@
     </row>
     <row r="33" ht="16.5" spans="1:5">
       <c r="A33" s="19" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="34" ht="16.5" spans="1:5">
       <c r="A34" s="20" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B34" s="20" t="s">
         <v>3</v>
@@ -2942,7 +2945,7 @@
         <v>4</v>
       </c>
       <c r="D34" s="20" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E34" s="20" t="s">
         <v>6</v>
@@ -2950,138 +2953,138 @@
     </row>
     <row r="35" ht="16.5" spans="1:5">
       <c r="A35" s="14" t="s">
-        <v>70</v>
+        <v>111</v>
       </c>
       <c r="B35" s="14" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D35" s="14" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="36" ht="16.5" spans="1:5">
       <c r="A36" s="14" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B36" s="14" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E36" s="14" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="37" ht="16.5" spans="1:5">
       <c r="A37" s="14" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B37" s="14" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D37" s="14" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E37" s="14" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="38" ht="16.5" spans="1:5">
       <c r="A38" s="14" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B38" s="14" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D38" s="14" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E38" s="14" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="40" ht="16.5" spans="1:5">
       <c r="A40" s="14" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B40" s="14" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E40" s="14" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="41" ht="16.5" spans="1:5">
       <c r="A41" s="14" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B41" s="14" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C41" s="14" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D41" s="14" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E41" s="14" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="42" ht="16.5" spans="1:5">
       <c r="A42" s="14" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B42" s="14" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D42" s="14" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E42" s="14" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="43" ht="16.5" spans="1:5">
       <c r="A43" s="14" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B43" s="14" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C43" s="14" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D43" s="14" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E43" s="14" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
   </sheetData>
@@ -3112,13 +3115,13 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1"/>
     <row r="5" ht="24" customHeight="1" spans="1:5">
       <c r="A5" s="16" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -3165,29 +3168,29 @@
       </c>
       <c r="B8" s="14"/>
       <c r="C8" s="12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:5">
       <c r="A9" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B9" s="13"/>
       <c r="C9" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:5">
       <c r="A10" s="13" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B10" s="13" t="s">
         <v>20</v>
@@ -3199,41 +3202,41 @@
         <v>26</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:5">
       <c r="A11" s="14" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B11" s="14" t="s">
         <v>8</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:5">
       <c r="A12" s="13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>53</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:5">
@@ -3244,30 +3247,30 @@
         <v>33</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D13" s="12" t="s">
         <v>35</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:5">
       <c r="A14" s="13" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B14" s="13" t="s">
         <v>8</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:5">
@@ -3281,7 +3284,7 @@
         <v>44</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E15" s="12" t="s">
         <v>11</v>
@@ -3318,7 +3321,7 @@
         <v>53</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:5">
@@ -3346,7 +3349,7 @@
     </row>
     <row r="22" ht="16.5" spans="1:5">
       <c r="A22" s="14" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B22" s="14" t="s">
         <v>64</v>
@@ -3355,7 +3358,7 @@
         <v>12</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E22" s="18" t="s">
         <v>11</v>
@@ -3363,16 +3366,16 @@
     </row>
     <row r="23" ht="16.5" spans="1:5">
       <c r="A23" s="14" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B23" s="14" t="s">
         <v>64</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E23" s="18" t="s">
         <v>11</v>
@@ -3380,7 +3383,7 @@
     </row>
     <row r="24" ht="16.5" spans="1:5">
       <c r="A24" s="14" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B24" s="14" t="s">
         <v>64</v>
@@ -3389,7 +3392,7 @@
         <v>42</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E24" s="18" t="s">
         <v>11</v>
@@ -3397,7 +3400,7 @@
     </row>
     <row r="25" ht="16.5" spans="1:5">
       <c r="A25" s="14" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B25" s="14" t="s">
         <v>64</v>
@@ -3406,7 +3409,7 @@
         <v>51</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E25" s="18" t="s">
         <v>11</v>
@@ -3414,16 +3417,16 @@
     </row>
     <row r="26" ht="33" spans="1:5">
       <c r="A26" s="14" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B26" s="14" t="s">
         <v>64</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E26" s="18" t="s">
         <v>11</v>
@@ -3455,13 +3458,13 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1"/>
     <row r="5" ht="24" customHeight="1" spans="1:5">
       <c r="A5" s="16" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -3499,50 +3502,50 @@
         <v>10</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:5">
       <c r="A8" s="14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B8" s="14"/>
       <c r="C8" s="12" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:5">
       <c r="A9" s="13" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B9" s="13"/>
       <c r="C9" s="8" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:5">
       <c r="A10" s="13" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B10" s="13" t="s">
         <v>106</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:5">
@@ -3553,13 +3556,13 @@
         <v>85</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D11" s="12" t="s">
         <v>26</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:5">
@@ -3570,64 +3573,64 @@
         <v>85</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>26</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:5">
       <c r="A13" s="14" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B13" s="14" t="s">
         <v>75</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D13" s="12" t="s">
         <v>35</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:5">
       <c r="A14" s="13" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B14" s="13" t="s">
         <v>85</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>35</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:5">
       <c r="A15" s="14" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B15" s="14" t="s">
         <v>13</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D15" s="12" t="s">
         <v>30</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:5">
@@ -3641,15 +3644,15 @@
         <v>44</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:5">
       <c r="A21" s="17" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -3658,37 +3661,37 @@
     </row>
     <row r="22" ht="16.5" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="25" ht="16.5" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="26" ht="16.5" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="27" ht="16.5" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="28" ht="16.5" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
   </sheetData>
@@ -3717,13 +3720,13 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1"/>
     <row r="5" ht="18" spans="1:5">
       <c r="A5" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -3732,92 +3735,92 @@
     </row>
     <row r="6" ht="33" spans="1:5">
       <c r="A6" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:5">
       <c r="A7" s="13" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C7" s="13" t="s">
         <v>12</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:5">
       <c r="A8" s="14" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:5">
       <c r="A9" s="13" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:5">
       <c r="A10" s="14" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:5">
       <c r="A13" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -3831,107 +3834,107 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="15" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="15" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="15" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="15" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="15" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="15" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="15" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="15" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="15" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="15" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="15" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="15" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="15" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="15" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="15" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="15" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="15" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="15" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="15" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="15" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="36" ht="16.5" spans="1:5">
@@ -3941,7 +3944,7 @@
     </row>
     <row r="39" ht="18" spans="1:5">
       <c r="A39" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -3950,92 +3953,92 @@
     </row>
     <row r="40" ht="33" spans="1:5">
       <c r="A40" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="41" ht="36" customHeight="1" spans="1:5">
       <c r="A41" s="8" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="42" ht="36" customHeight="1" spans="1:5">
       <c r="A42" s="12" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B42" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="C42" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="D42" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="E42" s="12" t="s">
         <v>273</v>
-      </c>
-      <c r="C42" s="12" t="s">
-        <v>274</v>
-      </c>
-      <c r="D42" s="12" t="s">
-        <v>271</v>
-      </c>
-      <c r="E42" s="12" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="43" ht="36" customHeight="1" spans="1:5">
       <c r="A43" s="8" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="44" ht="36" customHeight="1" spans="1:5">
       <c r="A44" s="12" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="47" ht="18" spans="1:5">
       <c r="A47" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
@@ -4049,167 +4052,167 @@
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="15" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="15" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="15" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="15" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="15" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="15" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="15" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="15" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="15" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="15" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="15" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="15" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="15" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="15" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="15" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="15" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="15" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="15" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="15" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="15" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="15" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="15" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="15" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="15" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="15" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="15" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="15" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="15" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="15" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="15" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="15" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="15" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="15" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="82" spans="1:1">
@@ -4301,12 +4304,12 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:5">
       <c r="A5" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -4315,57 +4318,57 @@
     </row>
     <row r="6" ht="16.5" spans="1:5">
       <c r="A6" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="7" ht="40" customHeight="1" spans="1:5">
       <c r="A7" s="5" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:5">
       <c r="A8" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="9" ht="40" customHeight="1" spans="1:5">
       <c r="A9" s="5" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:5">
       <c r="A10" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="11" ht="40" customHeight="1" spans="1:5">
       <c r="A11" s="5" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:5">
       <c r="A12" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="13" ht="40" customHeight="1" spans="1:5">
       <c r="A13" s="5" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:5">
       <c r="A14" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="15" ht="40" customHeight="1" spans="1:5">
       <c r="A15" s="5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:5">
       <c r="A18" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -4374,77 +4377,77 @@
     </row>
     <row r="19" ht="16.5" spans="1:5">
       <c r="A19" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="20" ht="50" customHeight="1" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:5">
       <c r="A21" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="22" ht="50" customHeight="1" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:5">
       <c r="A23" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="24" ht="50" customHeight="1" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="25" ht="16.5" spans="1:5">
       <c r="A25" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="26" ht="50" customHeight="1" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="27" ht="16.5" spans="1:5">
       <c r="A27" s="4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="28" ht="50" customHeight="1" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="29" ht="16.5" spans="1:5">
       <c r="A29" s="4" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="30" ht="50" customHeight="1" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="31" ht="16.5" spans="1:5">
       <c r="A31" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="32" ht="50" customHeight="1" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="35" ht="18" spans="1:5">
       <c r="A35" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -4453,81 +4456,81 @@
     </row>
     <row r="36" ht="16.5" spans="1:5">
       <c r="A36" s="6" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="37" ht="36" customHeight="1" spans="1:5">
       <c r="A37" s="7" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="10"/>
     </row>
     <row r="38" ht="36" customHeight="1" spans="1:5">
       <c r="A38" s="11" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C38" s="9"/>
       <c r="D38" s="10"/>
     </row>
     <row r="39" ht="36" customHeight="1" spans="1:5">
       <c r="A39" s="7" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="10"/>
     </row>
     <row r="40" ht="36" customHeight="1" spans="1:5">
       <c r="A40" s="11" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C40" s="9"/>
       <c r="D40" s="10"/>
     </row>
     <row r="41" ht="36" customHeight="1" spans="1:5">
       <c r="A41" s="7" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="10"/>
     </row>
     <row r="42" ht="36" customHeight="1" spans="1:5">
       <c r="A42" s="11" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C42" s="9"/>
       <c r="D42" s="10"/>
     </row>
     <row r="43" ht="36" customHeight="1" spans="1:5">
       <c r="A43" s="7" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="10"/>

--- a/docs/database/人间烟火_数据库设计文档.xlsx
+++ b/docs/database/人间烟火_数据库设计文档.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="343">
   <si>
     <t>用户管理</t>
   </si>
@@ -362,42 +362,6 @@
   </si>
   <si>
     <t>每次获取详情时自动 +1,用于做推荐算法</t>
-  </si>
-  <si>
-    <t>idx_encyclopedia_name</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>加速按菜名搜索</t>
-  </si>
-  <si>
-    <t>idx_encyclopedia_category</t>
-  </si>
-  <si>
-    <t>加速按分类筛选</t>
-  </si>
-  <si>
-    <t>idx_encyclopedia_external</t>
-  </si>
-  <si>
-    <t>(external_source, external_id)</t>
-  </si>
-  <si>
-    <t>防止外部数据重复导入</t>
-  </si>
-  <si>
-    <t>ft_encyclopedia_name_desc</t>
-  </si>
-  <si>
-    <t>FULLTEXT</t>
-  </si>
-  <si>
-    <t>(name, description)</t>
-  </si>
-  <si>
-    <t>MySQL 全文索引，支持中文分词搜索</t>
   </si>
   <si>
     <t>JSON 字段结构说明</t>
@@ -421,6 +385,9 @@
   </si>
   <si>
     <t>必填</t>
+  </si>
+  <si>
+    <t>name</t>
   </si>
   <si>
     <t>string</t>
@@ -2536,10 +2503,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="1" max="1" width="23.8166666666667" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
@@ -2829,270 +2796,178 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" ht="18" spans="1:5">
-      <c r="A24" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-    </row>
-    <row r="25" ht="16.5" spans="1:5">
-      <c r="A25" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B25" s="6" t="s">
+    <row r="26" ht="18" spans="1:5">
+      <c r="A26" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+    </row>
+    <row r="27" ht="16.5" spans="1:5">
+      <c r="A27" s="19" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="28" ht="16.5" spans="1:5">
+      <c r="A28" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="B28" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="C25" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="D25" s="6" t="s">
+      <c r="C28" s="20" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="26" ht="16.5" spans="1:5">
-      <c r="A26" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="B26" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="C26" s="14" t="s">
-        <v>111</v>
-      </c>
-      <c r="D26" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="E26" s="18" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="27" ht="16.5" spans="1:5">
-      <c r="A27" s="14" t="s">
+      <c r="D28" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="B27" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="C27" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="D27" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="E27" s="18" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="28" ht="16.5" spans="1:5">
-      <c r="A28" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="B28" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C28" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="D28" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="E28" s="18" t="s">
-        <v>11</v>
+      <c r="E28" s="20" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="29" ht="16.5" spans="1:5">
       <c r="A29" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="C29" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="E29" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="B29" s="14" t="s">
+    </row>
+    <row r="30" ht="16.5" spans="1:5">
+      <c r="A30" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="C29" s="14" t="s">
+      <c r="B30" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D29" s="14" t="s">
+      <c r="C30" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="E29" s="18" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="32" ht="18" spans="1:5">
-      <c r="A32" s="2" t="s">
+      <c r="D30" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="E30" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-    </row>
-    <row r="33" ht="16.5" spans="1:5">
-      <c r="A33" s="19" t="s">
+    </row>
+    <row r="31" ht="16.5" spans="1:5">
+      <c r="A31" s="14" t="s">
         <v>123</v>
       </c>
+      <c r="B31" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="C31" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="D31" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="E31" s="14" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="32" ht="16.5" spans="1:5">
+      <c r="A32" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="B32" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="D32" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="E32" s="14" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="34" ht="16.5" spans="1:5">
-      <c r="A34" s="20" t="s">
-        <v>124</v>
-      </c>
-      <c r="B34" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="C34" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="D34" s="20" t="s">
-        <v>125</v>
-      </c>
-      <c r="E34" s="20" t="s">
-        <v>6</v>
+      <c r="A34" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="B34" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="C34" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="D34" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="E34" s="14" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="35" ht="16.5" spans="1:5">
       <c r="A35" s="14" t="s">
-        <v>111</v>
+        <v>134</v>
       </c>
       <c r="B35" s="14" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D35" s="14" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
     </row>
     <row r="36" ht="16.5" spans="1:5">
       <c r="A36" s="14" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="B36" s="14" t="s">
         <v>131</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="D36" s="14" t="s">
         <v>128</v>
       </c>
       <c r="E36" s="14" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
     </row>
     <row r="37" ht="16.5" spans="1:5">
       <c r="A37" s="14" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="B37" s="14" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D37" s="14" t="s">
         <v>128</v>
       </c>
       <c r="E37" s="14" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="38" ht="16.5" spans="1:5">
-      <c r="A38" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="B38" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="C38" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="D38" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="E38" s="14" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="40" ht="16.5" spans="1:5">
-      <c r="A40" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="B40" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="C40" s="14" t="s">
-        <v>143</v>
-      </c>
-      <c r="D40" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="E40" s="14" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="41" ht="16.5" spans="1:5">
-      <c r="A41" s="14" t="s">
-        <v>145</v>
-      </c>
-      <c r="B41" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="C41" s="14" t="s">
-        <v>146</v>
-      </c>
-      <c r="D41" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="E41" s="14" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="42" ht="16.5" spans="1:5">
-      <c r="A42" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="B42" s="14" t="s">
-        <v>142</v>
-      </c>
-      <c r="C42" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="D42" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="E42" s="14" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="43" ht="16.5" spans="1:5">
-      <c r="A43" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="B43" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="C43" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="D43" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="E43" s="14" t="s">
-        <v>153</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="A32:E32"/>
-    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A27:E27"/>
     <mergeCell ref="A1:E2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3115,13 +2990,13 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1"/>
     <row r="5" ht="24" customHeight="1" spans="1:5">
       <c r="A5" s="16" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -3168,29 +3043,29 @@
       </c>
       <c r="B8" s="14"/>
       <c r="C8" s="12" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:5">
       <c r="A9" s="13" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="B9" s="13"/>
       <c r="C9" s="8" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:5">
       <c r="A10" s="13" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="B10" s="13" t="s">
         <v>20</v>
@@ -3202,41 +3077,41 @@
         <v>26</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:5">
       <c r="A11" s="14" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="B11" s="14" t="s">
         <v>8</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:5">
       <c r="A12" s="13" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>53</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:5">
@@ -3247,30 +3122,30 @@
         <v>33</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="D13" s="12" t="s">
         <v>35</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:5">
       <c r="A14" s="13" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="B14" s="13" t="s">
         <v>8</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:5">
@@ -3284,7 +3159,7 @@
         <v>44</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="E15" s="12" t="s">
         <v>11</v>
@@ -3321,7 +3196,7 @@
         <v>53</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:5">
@@ -3349,7 +3224,7 @@
     </row>
     <row r="22" ht="16.5" spans="1:5">
       <c r="A22" s="14" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="B22" s="14" t="s">
         <v>64</v>
@@ -3358,7 +3233,7 @@
         <v>12</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="E22" s="18" t="s">
         <v>11</v>
@@ -3366,16 +3241,16 @@
     </row>
     <row r="23" ht="16.5" spans="1:5">
       <c r="A23" s="14" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="B23" s="14" t="s">
         <v>64</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="E23" s="18" t="s">
         <v>11</v>
@@ -3383,7 +3258,7 @@
     </row>
     <row r="24" ht="16.5" spans="1:5">
       <c r="A24" s="14" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="B24" s="14" t="s">
         <v>64</v>
@@ -3392,7 +3267,7 @@
         <v>42</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="E24" s="18" t="s">
         <v>11</v>
@@ -3400,7 +3275,7 @@
     </row>
     <row r="25" ht="16.5" spans="1:5">
       <c r="A25" s="14" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="B25" s="14" t="s">
         <v>64</v>
@@ -3409,7 +3284,7 @@
         <v>51</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="E25" s="18" t="s">
         <v>11</v>
@@ -3417,16 +3292,16 @@
     </row>
     <row r="26" ht="33" spans="1:5">
       <c r="A26" s="14" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="B26" s="14" t="s">
         <v>64</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="E26" s="18" t="s">
         <v>11</v>
@@ -3458,13 +3333,13 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1"/>
     <row r="5" ht="24" customHeight="1" spans="1:5">
       <c r="A5" s="16" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -3502,50 +3377,50 @@
         <v>10</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:5">
       <c r="A8" s="14" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="B8" s="14"/>
       <c r="C8" s="12" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:5">
       <c r="A9" s="13" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="B9" s="13"/>
       <c r="C9" s="8" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:5">
       <c r="A10" s="13" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="B10" s="13" t="s">
         <v>106</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:5">
@@ -3556,13 +3431,13 @@
         <v>85</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="D11" s="12" t="s">
         <v>26</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:5">
@@ -3573,64 +3448,64 @@
         <v>85</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>26</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:5">
       <c r="A13" s="14" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="B13" s="14" t="s">
         <v>75</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="D13" s="12" t="s">
         <v>35</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:5">
       <c r="A14" s="13" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="B14" s="13" t="s">
         <v>85</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>35</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:5">
       <c r="A15" s="14" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="B15" s="14" t="s">
         <v>13</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="D15" s="12" t="s">
         <v>30</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:5">
@@ -3644,15 +3519,15 @@
         <v>44</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:5">
       <c r="A21" s="17" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -3661,37 +3536,37 @@
     </row>
     <row r="22" ht="16.5" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
     </row>
     <row r="25" ht="16.5" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
     </row>
     <row r="26" ht="16.5" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
     </row>
     <row r="27" ht="16.5" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
     </row>
     <row r="28" ht="16.5" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
     </row>
   </sheetData>
@@ -3720,13 +3595,13 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1"/>
     <row r="5" ht="18" spans="1:5">
       <c r="A5" s="2" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -3735,92 +3610,92 @@
     </row>
     <row r="6" ht="33" spans="1:5">
       <c r="A6" s="6" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:5">
       <c r="A7" s="13" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="C7" s="13" t="s">
         <v>12</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:5">
       <c r="A8" s="14" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:5">
       <c r="A9" s="13" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:5">
       <c r="A10" s="14" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:5">
       <c r="A13" s="2" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -3834,107 +3709,107 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="15" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="15" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="15" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="15" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="15" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="15" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="15" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="15" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="15" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="15" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="15" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="15" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="15" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="15" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="15" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="15" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="15" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="15" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="15" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="15" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="15" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
     </row>
     <row r="36" ht="16.5" spans="1:5">
@@ -3944,7 +3819,7 @@
     </row>
     <row r="39" ht="18" spans="1:5">
       <c r="A39" s="2" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -3953,92 +3828,92 @@
     </row>
     <row r="40" ht="33" spans="1:5">
       <c r="A40" s="6" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
     </row>
     <row r="41" ht="36" customHeight="1" spans="1:5">
       <c r="A41" s="8" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
     </row>
     <row r="42" ht="36" customHeight="1" spans="1:5">
       <c r="A42" s="12" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
     </row>
     <row r="43" ht="36" customHeight="1" spans="1:5">
       <c r="A43" s="8" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
     </row>
     <row r="44" ht="36" customHeight="1" spans="1:5">
       <c r="A44" s="12" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
     </row>
     <row r="47" ht="18" spans="1:5">
       <c r="A47" s="2" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
@@ -4052,167 +3927,167 @@
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="15" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="15" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="15" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="15" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="15" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="15" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="15" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="15" t="s">
-        <v>287</v>
+        <v>276</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="15" t="s">
-        <v>288</v>
+        <v>277</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="15" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="15" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="15" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="15" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="15" t="s">
-        <v>293</v>
+        <v>282</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="15" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="15" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="15" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="15" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="15" t="s">
-        <v>297</v>
+        <v>286</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="15" t="s">
-        <v>298</v>
+        <v>287</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="15" t="s">
-        <v>299</v>
+        <v>288</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="15" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="15" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="15" t="s">
-        <v>301</v>
+        <v>290</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="15" t="s">
-        <v>302</v>
+        <v>291</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="15" t="s">
-        <v>303</v>
+        <v>292</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="15" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="15" t="s">
-        <v>304</v>
+        <v>293</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="15" t="s">
-        <v>305</v>
+        <v>294</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="15" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="15" t="s">
-        <v>307</v>
+        <v>296</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="15" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="15" t="s">
-        <v>308</v>
+        <v>297</v>
       </c>
     </row>
     <row r="82" spans="1:1">
@@ -4304,12 +4179,12 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>309</v>
+        <v>298</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:5">
       <c r="A5" s="2" t="s">
-        <v>310</v>
+        <v>299</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -4318,57 +4193,57 @@
     </row>
     <row r="6" ht="16.5" spans="1:5">
       <c r="A6" s="4" t="s">
-        <v>311</v>
+        <v>300</v>
       </c>
     </row>
     <row r="7" ht="40" customHeight="1" spans="1:5">
       <c r="A7" s="5" t="s">
-        <v>312</v>
+        <v>301</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:5">
       <c r="A8" s="4" t="s">
-        <v>313</v>
+        <v>302</v>
       </c>
     </row>
     <row r="9" ht="40" customHeight="1" spans="1:5">
       <c r="A9" s="5" t="s">
-        <v>314</v>
+        <v>303</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:5">
       <c r="A10" s="4" t="s">
-        <v>315</v>
+        <v>304</v>
       </c>
     </row>
     <row r="11" ht="40" customHeight="1" spans="1:5">
       <c r="A11" s="5" t="s">
-        <v>316</v>
+        <v>305</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:5">
       <c r="A12" s="4" t="s">
-        <v>317</v>
+        <v>306</v>
       </c>
     </row>
     <row r="13" ht="40" customHeight="1" spans="1:5">
       <c r="A13" s="5" t="s">
-        <v>318</v>
+        <v>307</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:5">
       <c r="A14" s="4" t="s">
-        <v>319</v>
+        <v>308</v>
       </c>
     </row>
     <row r="15" ht="40" customHeight="1" spans="1:5">
       <c r="A15" s="5" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:5">
       <c r="A18" s="2" t="s">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -4377,77 +4252,77 @@
     </row>
     <row r="19" ht="16.5" spans="1:5">
       <c r="A19" s="4" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
     </row>
     <row r="20" ht="50" customHeight="1" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:5">
       <c r="A21" s="4" t="s">
-        <v>324</v>
+        <v>313</v>
       </c>
     </row>
     <row r="22" ht="50" customHeight="1" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:5">
       <c r="A23" s="4" t="s">
-        <v>326</v>
+        <v>315</v>
       </c>
     </row>
     <row r="24" ht="50" customHeight="1" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>327</v>
+        <v>316</v>
       </c>
     </row>
     <row r="25" ht="16.5" spans="1:5">
       <c r="A25" s="4" t="s">
-        <v>328</v>
+        <v>317</v>
       </c>
     </row>
     <row r="26" ht="50" customHeight="1" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>329</v>
+        <v>318</v>
       </c>
     </row>
     <row r="27" ht="16.5" spans="1:5">
       <c r="A27" s="4" t="s">
-        <v>330</v>
+        <v>319</v>
       </c>
     </row>
     <row r="28" ht="50" customHeight="1" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>331</v>
+        <v>320</v>
       </c>
     </row>
     <row r="29" ht="16.5" spans="1:5">
       <c r="A29" s="4" t="s">
-        <v>332</v>
+        <v>321</v>
       </c>
     </row>
     <row r="30" ht="50" customHeight="1" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>333</v>
+        <v>322</v>
       </c>
     </row>
     <row r="31" ht="16.5" spans="1:5">
       <c r="A31" s="4" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
     </row>
     <row r="32" ht="50" customHeight="1" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>335</v>
+        <v>324</v>
       </c>
     </row>
     <row r="35" ht="18" spans="1:5">
       <c r="A35" s="2" t="s">
-        <v>336</v>
+        <v>325</v>
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -4456,81 +4331,81 @@
     </row>
     <row r="36" ht="16.5" spans="1:5">
       <c r="A36" s="6" t="s">
-        <v>337</v>
+        <v>326</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>339</v>
+        <v>328</v>
       </c>
     </row>
     <row r="37" ht="36" customHeight="1" spans="1:5">
       <c r="A37" s="7" t="s">
-        <v>340</v>
+        <v>329</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>341</v>
+        <v>330</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="10"/>
     </row>
     <row r="38" ht="36" customHeight="1" spans="1:5">
       <c r="A38" s="11" t="s">
-        <v>342</v>
+        <v>331</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="C38" s="9"/>
       <c r="D38" s="10"/>
     </row>
     <row r="39" ht="36" customHeight="1" spans="1:5">
       <c r="A39" s="7" t="s">
-        <v>344</v>
+        <v>333</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>345</v>
+        <v>334</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="10"/>
     </row>
     <row r="40" ht="36" customHeight="1" spans="1:5">
       <c r="A40" s="11" t="s">
-        <v>346</v>
+        <v>335</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>347</v>
+        <v>336</v>
       </c>
       <c r="C40" s="9"/>
       <c r="D40" s="10"/>
     </row>
     <row r="41" ht="36" customHeight="1" spans="1:5">
       <c r="A41" s="7" t="s">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>349</v>
+        <v>338</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="10"/>
     </row>
     <row r="42" ht="36" customHeight="1" spans="1:5">
       <c r="A42" s="11" t="s">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>351</v>
+        <v>340</v>
       </c>
       <c r="C42" s="9"/>
       <c r="D42" s="10"/>
     </row>
     <row r="43" ht="36" customHeight="1" spans="1:5">
       <c r="A43" s="7" t="s">
-        <v>352</v>
+        <v>341</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>353</v>
+        <v>342</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="10"/>
